--- a/PRUEBAS A CALIFICAR/Ya procesadas/COLEGIO ALEJANDRO OBREGON-703_20260625_102348.xlsx
+++ b/PRUEBAS A CALIFICAR/Ya procesadas/COLEGIO ALEJANDRO OBREGON-703_20260625_102348.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Catherine Espinosa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Catherine Espinosa\Desktop\PROYECTO JULIANA\PRUEBAS A CALIFICAR\Ya procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B66B3A0-49D2-48D5-832A-88F0401AEB19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
